--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260610.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260610.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>202606WTEM6F</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>598,600</t>
+          <t>76</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>202606WTEM6F</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>598,600</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>798,897</t>
+          <t>1,534,384</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,534,384</t>
+          <t>798,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>145,386</t>
+          <t>3,349,981</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>3,349,981</t>
+          <t>145,386</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,186,076</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>202606WVHFM6F</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>179,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>828,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>202606WVHFM6F</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>179,000</t>
+          <t>269</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>828,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>1,186,076</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>1,542,400</t>
+          <t>294,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>294,000</t>
+          <t>1,542,400</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>485,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>485,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
